--- a/doc/STAYTRUE 模块.xlsx
+++ b/doc/STAYTRUE 模块.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12075"/>
+    <workbookView windowWidth="27945" windowHeight="12525"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -26,8 +26,180 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_FCA8D8532DDC4C3381400151C98ECB77"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1066800" y="1898015"/>
+          <a:ext cx="1685925" cy="1061085"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="ID_8FC5AA2F27A04D949F9046733972C903" descr="图片_007_02"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3028950" y="2076450"/>
+          <a:ext cx="10055860" cy="8890000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="ID_2CE9553C031349D685802DD5BC3C3607" descr="SDC-LE-A3L"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7051675" y="1898015"/>
+          <a:ext cx="4107180" cy="2462530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="ID_959B9784CBF94FC08153250204378FB1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10730865" y="2371725"/>
+          <a:ext cx="2055495" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="ID_CD677FDE9AD544F9A4B7E596CAA1A1AF"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8933815" y="2505075"/>
+          <a:ext cx="1134745" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_73837BFFBB3F469987684A7F080C00E2"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7" r:link="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5031105" y="2352675"/>
+          <a:ext cx="1434465" cy="1085850"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="ID_DFBF1F7DEF7D440280A1D3C0FB247278" descr="正面"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13673455" y="2695575"/>
+          <a:ext cx="10055860" cy="6601460"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="34">
   <si>
     <t>健身器材模块</t>
   </si>
@@ -53,6 +225,12 @@
     <t>SDC-LE-05</t>
   </si>
   <si>
+    <t>SDC-LE-05HD</t>
+  </si>
+  <si>
+    <t>SDC-LE-05HS</t>
+  </si>
+  <si>
     <t>SDC-HR-P01</t>
   </si>
   <si>
@@ -78,19 +256,26 @@
   </si>
   <si>
     <t>单模(BLE)，插件模组
-串口接口支持5V</t>
+支持5V供电及串口</t>
   </si>
   <si>
     <t>单模(BLE)，引脚引出，支持SDK 开发 拓展其他项目</t>
   </si>
   <si>
     <t>单模(BLE)，引脚引出，支持SDK 开发 拓展其他项目
-串口接口支持5V</t>
+支持5V供电及串口</t>
   </si>
   <si>
     <t>双模(BT/BLE)支持音频引脚全部引出，支持SDK开发 拓展其他项目</t>
   </si>
   <si>
+    <t>双模(BT/BLE)支持音频，支持SDK开发 拓展其他项目
+支持5V供电及串口</t>
+  </si>
+  <si>
+    <t>双模(BT/BLE)支持音频，支持5V供电及串口</t>
+  </si>
+  <si>
     <t>模组内置算法，串口通信，直接输出心率值</t>
   </si>
   <si>
@@ -115,7 +300,7 @@
     <t>BQB、SRRC、FCC ID、CE RED、NCC</t>
   </si>
   <si>
-    <t xml:space="preserve">BQB、SRRC、FCC ID、CE RED </t>
+    <t>BQB、SRRC、FCC ID、CE RED</t>
   </si>
   <si>
     <t>产品图片</t>
@@ -1049,197 +1234,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>12625</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1685925" cy="1060600"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1066800" y="1898015"/>
-          <a:ext cx="1685925" cy="1061085"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>541068</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="689514" cy="1085850"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3539490" y="1885950"/>
-          <a:ext cx="688975" cy="1085850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>168429</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1434791" cy="1085850"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="3"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5191760" y="1885950"/>
-          <a:ext cx="1434465" cy="1085850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>128999</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1524000" cy="827851"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="4"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7048500" y="2014855"/>
-          <a:ext cx="1524000" cy="827405"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>251745</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1134809" cy="1085850"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="5"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId6" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="9036685" y="1885950"/>
-          <a:ext cx="1134745" cy="1085850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>315197</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2055655" cy="1085850"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="6"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId7" r:link="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10970895" y="1885950"/>
-          <a:ext cx="2055495" cy="1085850"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
@@ -1478,25 +1472,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="18" customHeight="1" outlineLevelRow="6"/>
   <cols>
-    <col min="2" max="2" width="25.35" style="1" customWidth="1"/>
-    <col min="3" max="4" width="26.575" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7916666666667" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.55" style="1" customWidth="1"/>
-    <col min="7" max="7" width="40.3333333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5916666666667" customWidth="1"/>
+    <col min="2" max="2" width="29.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.0666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.5916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:8">
+    <row r="1" ht="16.5" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" ht="16.5" spans="1:8">
+    <row r="2" ht="16.5" spans="1:10">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1521,122 +1518,175 @@
       <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" ht="16.5" spans="1:8">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" ht="49.5" spans="1:8">
+    <row r="4" ht="66" spans="1:10">
       <c r="A4" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" ht="16.5" spans="1:8">
+    <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="6" ht="33" spans="1:8">
+    <row r="6" ht="33" spans="1:10">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>13</v>
+        <v>32</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="7" ht="85.5" customHeight="1" spans="1:8">
+    <row r="7" ht="85.5" customHeight="1" spans="1:10">
       <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7"/>
-    </row>
-    <row r="8" ht="36" customHeight="1" spans="1:8">
-      <c r="A8" s="3"/>
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_FCA8D8532DDC4C3381400151C98ECB77",1)</f>
+        <v>=DISPIMG("ID_FCA8D8532DDC4C3381400151C98ECB77",1)</v>
+      </c>
+      <c r="C7" t="str">
+        <f>_xlfn.DISPIMG("ID_8FC5AA2F27A04D949F9046733972C903",1)</f>
+        <v>=DISPIMG("ID_8FC5AA2F27A04D949F9046733972C903",1)</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_73837BFFBB3F469987684A7F080C00E2",1)</f>
+        <v>=DISPIMG("ID_73837BFFBB3F469987684A7F080C00E2",1)</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_2CE9553C031349D685802DD5BC3C3607",1)</f>
+        <v>=DISPIMG("ID_2CE9553C031349D685802DD5BC3C3607",1)</v>
+      </c>
+      <c r="F7" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_CD677FDE9AD544F9A4B7E596CAA1A1AF",1)</f>
+        <v>=DISPIMG("ID_CD677FDE9AD544F9A4B7E596CAA1A1AF",1)</v>
+      </c>
+      <c r="G7" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_959B9784CBF94FC08153250204378FB1",1)</f>
+        <v>=DISPIMG("ID_959B9784CBF94FC08153250204378FB1",1)</v>
+      </c>
+      <c r="I7" s="1" t="str">
+        <f>_xlfn.DISPIMG("ID_DFBF1F7DEF7D440280A1D3C0FB247278",1)</f>
+        <v>=DISPIMG("ID_DFBF1F7DEF7D440280A1D3C0FB247278",1)</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>